--- a/Arquivos novos.xlsx
+++ b/Arquivos novos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ADICEL-APP01\Publica\2. FICHAS TÉCNICAS ADICEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2484D149-BCF7-4CED-9AE6-A6E1AC97C878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471A4883-7456-4D87-9CA3-0232B9381FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{ED76BE6E-8505-4BA8-BADA-DAC31AD5EC9A}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$353</definedName>
     <definedName name="DadosExternos_1" localSheetId="1" hidden="1">pw_produtos_estoque!$A$1:$E$396</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
